--- a/02_加值成品/八下/八下5-1_三種難度測驗卷.xlsx
+++ b/02_加值成品/八下/八下5-1_三種難度測驗卷.xlsx
@@ -490,19 +490,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="62" customWidth="1" min="2" max="2"/>
+    <col width="54" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="42" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>國二下學期 八下5-1 認識有機化合物　測驗　★☆☆ 基礎（記憶・理解）</t>
+          <t>國二下學期 八下5-1 認識有機化合物　測驗　★☆☆ 基礎（記憶・理解）（四選一單選）</t>
         </is>
       </c>
     </row>
@@ -519,16 +523,36 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
+          <t>(A)</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>(B)</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>(C)</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>(D)</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
           <t>答案</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>解析</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="34" customHeight="1">
+    <row r="3" ht="40" customHeight="1">
       <c r="A3" s="3" t="n">
         <v>1</v>
       </c>
@@ -537,18 +561,38 @@
           <t>有機化合物以什麼為主體？</t>
         </is>
       </c>
-      <c r="C3" s="5" t="inlineStr">
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>物質多樣性</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
         <is>
           <t>碳</t>
         </is>
       </c>
-      <c r="D3" s="4" t="inlineStr">
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>不會</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>碳化</t>
+        </is>
+      </c>
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
         <is>
           <t>含碳</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="34" customHeight="1">
+    <row r="4" ht="40" customHeight="1">
       <c r="A4" s="6" t="n">
         <v>2</v>
       </c>
@@ -557,18 +601,38 @@
           <t>有機物多含碳和？</t>
         </is>
       </c>
-      <c r="C4" s="8" t="inlineStr">
+      <c r="C4" s="7" t="inlineStr">
+        <is>
+          <t>碳(碳化)</t>
+        </is>
+      </c>
+      <c r="D4" s="7" t="inlineStr">
+        <is>
+          <t>焦黑碳化</t>
+        </is>
+      </c>
+      <c r="E4" s="7" t="inlineStr">
         <is>
           <t>氫</t>
         </is>
       </c>
-      <c r="D4" s="7" t="inlineStr">
+      <c r="F4" s="7" t="inlineStr">
+        <is>
+          <t>無機</t>
+        </is>
+      </c>
+      <c r="G4" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H4" s="7" t="inlineStr">
         <is>
           <t>碳氫</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="34" customHeight="1">
+    <row r="5" ht="40" customHeight="1">
       <c r="A5" s="3" t="n">
         <v>3</v>
       </c>
@@ -577,18 +641,38 @@
           <t>麵粉加熱會？</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>物質多樣性</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>鍵結</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>碳化</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
         <is>
           <t>焦黑碳化</t>
         </is>
       </c>
-      <c r="D5" s="4" t="inlineStr">
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
         <is>
           <t>有機</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="34" customHeight="1">
+    <row r="6" ht="40" customHeight="1">
       <c r="A6" s="6" t="n">
         <v>4</v>
       </c>
@@ -597,18 +681,38 @@
           <t>食鹽加熱會碳化嗎？</t>
         </is>
       </c>
-      <c r="C6" s="8" t="inlineStr">
+      <c r="C6" s="7" t="inlineStr">
         <is>
           <t>不會</t>
         </is>
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
+          <t>碳氫氧氮</t>
+        </is>
+      </c>
+      <c r="E6" s="7" t="inlineStr">
+        <is>
+          <t>長鏈或環</t>
+        </is>
+      </c>
+      <c r="F6" s="7" t="inlineStr">
+        <is>
+          <t>碳(碳化)</t>
+        </is>
+      </c>
+      <c r="G6" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H6" s="7" t="inlineStr">
+        <is>
           <t>無機</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="34" customHeight="1">
+    <row r="7" ht="40" customHeight="1">
       <c r="A7" s="3" t="n">
         <v>5</v>
       </c>
@@ -617,18 +721,38 @@
           <t>碳原子能互相？</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>無機</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>不會</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
         <is>
           <t>鍵結</t>
         </is>
       </c>
-      <c r="D7" s="4" t="inlineStr">
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>碳化</t>
+        </is>
+      </c>
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
         <is>
           <t>成鏈</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="34" customHeight="1">
+    <row r="8" ht="40" customHeight="1">
       <c r="A8" s="6" t="n">
         <v>6</v>
       </c>
@@ -637,18 +761,38 @@
           <t>碳化變黑代表含？</t>
         </is>
       </c>
-      <c r="C8" s="8" t="inlineStr">
+      <c r="C8" s="7" t="inlineStr">
         <is>
           <t>碳</t>
         </is>
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
+          <t>焦黑(碳化)</t>
+        </is>
+      </c>
+      <c r="E8" s="7" t="inlineStr">
+        <is>
+          <t>不會</t>
+        </is>
+      </c>
+      <c r="F8" s="7" t="inlineStr">
+        <is>
+          <t>焦黑碳化</t>
+        </is>
+      </c>
+      <c r="G8" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H8" s="7" t="inlineStr">
+        <is>
           <t>有機物</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="34" customHeight="1">
+    <row r="9" ht="40" customHeight="1">
       <c r="A9" s="3" t="n">
         <v>7</v>
       </c>
@@ -657,18 +801,38 @@
           <t>糖加熱變成焦糖是？</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr">
         <is>
           <t>碳化</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
+          <t>碳氫氧氮</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>不會</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>燃燒</t>
+        </is>
+      </c>
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
+        <is>
           <t>有機</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="34" customHeight="1">
+    <row r="10" ht="40" customHeight="1">
       <c r="A10" s="6" t="n">
         <v>8</v>
       </c>
@@ -677,18 +841,38 @@
           <t>有機物多半可以？</t>
         </is>
       </c>
-      <c r="C10" s="8" t="inlineStr">
+      <c r="C10" s="7" t="inlineStr">
         <is>
           <t>燃燒</t>
         </is>
       </c>
       <c r="D10" s="7" t="inlineStr">
         <is>
+          <t>氫</t>
+        </is>
+      </c>
+      <c r="E10" s="7" t="inlineStr">
+        <is>
+          <t>長鏈或環</t>
+        </is>
+      </c>
+      <c r="F10" s="7" t="inlineStr">
+        <is>
+          <t>焦黑(碳化)</t>
+        </is>
+      </c>
+      <c r="G10" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H10" s="7" t="inlineStr">
+        <is>
           <t>可燃</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="34" customHeight="1">
+    <row r="11" ht="40" customHeight="1">
       <c r="A11" s="3" t="n">
         <v>9</v>
       </c>
@@ -697,18 +881,38 @@
           <t>有機化合物主要含哪種元素？</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr">
         <is>
           <t>碳</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
+          <t>無機</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>焦黑(碳化)</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>焦黑碳化</t>
+        </is>
+      </c>
+      <c r="G11" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
+        <is>
           <t>含碳</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="34" customHeight="1">
+    <row r="12" ht="40" customHeight="1">
       <c r="A12" s="6" t="n">
         <v>10</v>
       </c>
@@ -717,12 +921,32 @@
           <t>麵粉加熱變黑是因為含？</t>
         </is>
       </c>
-      <c r="C12" s="8" t="inlineStr">
+      <c r="C12" s="7" t="inlineStr">
         <is>
           <t>碳(碳化)</t>
         </is>
       </c>
       <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>無機物</t>
+        </is>
+      </c>
+      <c r="E12" s="7" t="inlineStr">
+        <is>
+          <t>無機</t>
+        </is>
+      </c>
+      <c r="F12" s="7" t="inlineStr">
+        <is>
+          <t>不會</t>
+        </is>
+      </c>
+      <c r="G12" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H12" s="7" t="inlineStr">
         <is>
           <t>有機</t>
         </is>
@@ -730,7 +954,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A1:H1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -742,19 +966,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="62" customWidth="1" min="2" max="2"/>
+    <col width="54" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="42" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>國二下學期 八下5-1 認識有機化合物　測驗　★★☆ 進階（應用・分析）</t>
+          <t>國二下學期 八下5-1 認識有機化合物　測驗　★★☆ 進階（應用・分析）（四選一單選）</t>
         </is>
       </c>
     </row>
@@ -771,16 +999,36 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
+          <t>(A)</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>(B)</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>(C)</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>(D)</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
           <t>答案</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>解析</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="34" customHeight="1">
+    <row r="3" ht="40" customHeight="1">
       <c r="A3" s="3" t="n">
         <v>1</v>
       </c>
@@ -789,18 +1037,38 @@
           <t>把糖粉在蒸發皿加熱觀察到？</t>
         </is>
       </c>
-      <c r="C3" s="5" t="inlineStr">
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>碳氫氧氮</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>燃燒</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>物質多樣性</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
         <is>
           <t>焦黑(碳化)</t>
         </is>
       </c>
-      <c r="D3" s="4" t="inlineStr">
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
         <is>
           <t>含碳</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="34" customHeight="1">
+    <row r="4" ht="40" customHeight="1">
       <c r="A4" s="6" t="n">
         <v>2</v>
       </c>
@@ -809,18 +1077,38 @@
           <t>食鹽在蒸發皿加熱觀察到？</t>
         </is>
       </c>
-      <c r="C4" s="8" t="inlineStr">
+      <c r="C4" s="7" t="inlineStr">
         <is>
           <t>不碳化(可能熔化)</t>
         </is>
       </c>
       <c r="D4" s="7" t="inlineStr">
         <is>
+          <t>通石灰水看是否變混濁</t>
+        </is>
+      </c>
+      <c r="E4" s="7" t="inlineStr">
+        <is>
+          <t>蒸發皿加熱看是否碳化</t>
+        </is>
+      </c>
+      <c r="F4" s="7" t="inlineStr">
+        <is>
+          <t>傳統分類將其歸無機</t>
+        </is>
+      </c>
+      <c r="G4" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H4" s="7" t="inlineStr">
+        <is>
           <t>無機</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="34" customHeight="1">
+    <row r="5" ht="40" customHeight="1">
       <c r="A5" s="3" t="n">
         <v>3</v>
       </c>
@@ -829,18 +1117,38 @@
           <t>碳能形成鏈與環造就？</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>燃燒</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>氫</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
         <is>
           <t>物質多樣性</t>
         </is>
       </c>
-      <c r="D5" s="4" t="inlineStr">
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>不會</t>
+        </is>
+      </c>
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
         <is>
           <t>種類多</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="34" customHeight="1">
+    <row r="6" ht="40" customHeight="1">
       <c r="A6" s="6" t="n">
         <v>4</v>
       </c>
@@ -849,18 +1157,38 @@
           <t>CO₂算有機還無機？</t>
         </is>
       </c>
-      <c r="C6" s="8" t="inlineStr">
+      <c r="C6" s="7" t="inlineStr">
+        <is>
+          <t>焦黑(碳化)</t>
+        </is>
+      </c>
+      <c r="D6" s="7" t="inlineStr">
         <is>
           <t>無機</t>
         </is>
       </c>
-      <c r="D6" s="7" t="inlineStr">
+      <c r="E6" s="7" t="inlineStr">
+        <is>
+          <t>碳</t>
+        </is>
+      </c>
+      <c r="F6" s="7" t="inlineStr">
+        <is>
+          <t>長鏈或環</t>
+        </is>
+      </c>
+      <c r="G6" s="8" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H6" s="7" t="inlineStr">
         <is>
           <t>歸類</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="34" customHeight="1">
+    <row r="7" ht="40" customHeight="1">
       <c r="A7" s="3" t="n">
         <v>5</v>
       </c>
@@ -869,18 +1197,38 @@
           <t>有機物常含哪些元素？</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>鍵結</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>不會</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>長鏈或環</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
         <is>
           <t>碳氫氧氮</t>
         </is>
       </c>
-      <c r="D7" s="4" t="inlineStr">
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
         <is>
           <t>組成</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="34" customHeight="1">
+    <row r="8" ht="40" customHeight="1">
       <c r="A8" s="6" t="n">
         <v>6</v>
       </c>
@@ -889,18 +1237,38 @@
           <t>酒精是有機物嗎？</t>
         </is>
       </c>
-      <c r="C8" s="8" t="inlineStr">
+      <c r="C8" s="7" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
+          <t>長鏈或環</t>
+        </is>
+      </c>
+      <c r="E8" s="7" t="inlineStr">
+        <is>
+          <t>不會</t>
+        </is>
+      </c>
+      <c r="F8" s="7" t="inlineStr">
+        <is>
+          <t>鍵結</t>
+        </is>
+      </c>
+      <c r="G8" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H8" s="7" t="inlineStr">
+        <is>
           <t>含碳</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="34" customHeight="1">
+    <row r="9" ht="40" customHeight="1">
       <c r="A9" s="3" t="n">
         <v>7</v>
       </c>
@@ -909,18 +1277,38 @@
           <t>塑膠屬有機還無機？</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>能與自身及他原子多重鍵結</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
         <is>
           <t>有機(聚合物)</t>
         </is>
       </c>
-      <c r="D9" s="4" t="inlineStr">
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>傳統分類將其歸無機</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>碳鍵結能力強可組多樣結構</t>
+        </is>
+      </c>
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
         <is>
           <t>含碳</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="34" customHeight="1">
+    <row r="10" ht="40" customHeight="1">
       <c r="A10" s="6" t="n">
         <v>8</v>
       </c>
@@ -929,18 +1317,38 @@
           <t>加熱碳化是哪類物質特徵？</t>
         </is>
       </c>
-      <c r="C10" s="8" t="inlineStr">
+      <c r="C10" s="7" t="inlineStr">
+        <is>
+          <t>氫</t>
+        </is>
+      </c>
+      <c r="D10" s="7" t="inlineStr">
         <is>
           <t>有機物</t>
         </is>
       </c>
-      <c r="D10" s="7" t="inlineStr">
+      <c r="E10" s="7" t="inlineStr">
+        <is>
+          <t>無機</t>
+        </is>
+      </c>
+      <c r="F10" s="7" t="inlineStr">
+        <is>
+          <t>焦黑碳化</t>
+        </is>
+      </c>
+      <c r="G10" s="8" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H10" s="7" t="inlineStr">
         <is>
           <t>特徵</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="34" customHeight="1">
+    <row r="11" ht="40" customHeight="1">
       <c r="A11" s="3" t="n">
         <v>9</v>
       </c>
@@ -949,18 +1357,38 @@
           <t>食鹽加熱不碳化因為它是？</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr">
         <is>
           <t>無機物</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>有機物</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>氫</t>
+        </is>
+      </c>
+      <c r="G11" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
+        <is>
           <t>無機</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="34" customHeight="1">
+    <row r="12" ht="40" customHeight="1">
       <c r="A12" s="6" t="n">
         <v>10</v>
       </c>
@@ -969,12 +1397,32 @@
           <t>碳原子能彼此鍵結形成？</t>
         </is>
       </c>
-      <c r="C12" s="8" t="inlineStr">
+      <c r="C12" s="7" t="inlineStr">
+        <is>
+          <t>焦黑碳化</t>
+        </is>
+      </c>
+      <c r="D12" s="7" t="inlineStr">
         <is>
           <t>長鏈或環</t>
         </is>
       </c>
-      <c r="D12" s="7" t="inlineStr">
+      <c r="E12" s="7" t="inlineStr">
+        <is>
+          <t>鍵結</t>
+        </is>
+      </c>
+      <c r="F12" s="7" t="inlineStr">
+        <is>
+          <t>燃燒</t>
+        </is>
+      </c>
+      <c r="G12" s="8" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H12" s="7" t="inlineStr">
         <is>
           <t>鍵結</t>
         </is>
@@ -982,7 +1430,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A1:H1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -994,19 +1442,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="62" customWidth="1" min="2" max="2"/>
+    <col width="54" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="42" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>國二下學期 八下5-1 認識有機化合物　測驗　★★★ 挑戰（評鑑・創造）</t>
+          <t>國二下學期 八下5-1 認識有機化合物　測驗　★★★ 挑戰（評鑑・創造）（四選一單選）</t>
         </is>
       </c>
     </row>
@@ -1023,16 +1475,36 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
+          <t>(A)</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>(B)</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>(C)</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>(D)</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
           <t>答案</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>解析</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="34" customHeight="1">
+    <row r="3" ht="40" customHeight="1">
       <c r="A3" s="3" t="n">
         <v>1</v>
       </c>
@@ -1041,18 +1513,38 @@
           <t>設計實驗辨別麵粉糖鹽三者用什麼方法？</t>
         </is>
       </c>
-      <c r="C3" s="5" t="inlineStr">
+      <c r="C3" s="4" t="inlineStr">
         <is>
           <t>蒸發皿加熱看是否碳化</t>
         </is>
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
+          <t>碳鍵結能力強可組多樣結構</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>前者含碳有機物,後者無機</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>含碳有機物加熱會碳化</t>
+        </is>
+      </c>
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
           <t>實驗</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="34" customHeight="1">
+    <row r="4" ht="40" customHeight="1">
       <c r="A4" s="6" t="n">
         <v>2</v>
       </c>
@@ -1061,18 +1553,38 @@
           <t>為何麵粉糖會碳化而鹽不會？</t>
         </is>
       </c>
-      <c r="C4" s="8" t="inlineStr">
+      <c r="C4" s="7" t="inlineStr">
+        <is>
+          <t>含碳氫可與氧反應放能</t>
+        </is>
+      </c>
+      <c r="D4" s="7" t="inlineStr">
         <is>
           <t>前者含碳有機物,後者無機</t>
         </is>
       </c>
-      <c r="D4" s="7" t="inlineStr">
+      <c r="E4" s="7" t="inlineStr">
+        <is>
+          <t>有機(聚合物)</t>
+        </is>
+      </c>
+      <c r="F4" s="7" t="inlineStr">
+        <is>
+          <t>不碳化(可能熔化)</t>
+        </is>
+      </c>
+      <c r="G4" s="8" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H4" s="7" t="inlineStr">
         <is>
           <t>組成</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="34" customHeight="1">
+    <row r="5" ht="40" customHeight="1">
       <c r="A5" s="3" t="n">
         <v>3</v>
       </c>
@@ -1081,18 +1593,38 @@
           <t>碳的哪個特性造就有機物種類繁多？</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C5" s="4" t="inlineStr">
         <is>
           <t>能與自身及他原子多重鍵結</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
+          <t>傳統分類將其歸無機</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>有機(聚合物)</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>不碳化(可能熔化)</t>
+        </is>
+      </c>
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
+        <is>
           <t>鍵結</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="34" customHeight="1">
+    <row r="6" ht="40" customHeight="1">
       <c r="A6" s="6" t="n">
         <v>4</v>
       </c>
@@ -1101,18 +1633,38 @@
           <t>為何CO₂不歸類有機物？</t>
         </is>
       </c>
-      <c r="C6" s="8" t="inlineStr">
+      <c r="C6" s="7" t="inlineStr">
+        <is>
+          <t>前者含碳有機物,後者無機</t>
+        </is>
+      </c>
+      <c r="D6" s="7" t="inlineStr">
+        <is>
+          <t>含碳有機物加熱會碳化</t>
+        </is>
+      </c>
+      <c r="E6" s="7" t="inlineStr">
+        <is>
+          <t>含碳氫可與氧反應放能</t>
+        </is>
+      </c>
+      <c r="F6" s="7" t="inlineStr">
         <is>
           <t>傳統分類將其歸無機</t>
         </is>
       </c>
-      <c r="D6" s="7" t="inlineStr">
+      <c r="G6" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H6" s="7" t="inlineStr">
         <is>
           <t>慣例</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="34" customHeight="1">
+    <row r="7" ht="40" customHeight="1">
       <c r="A7" s="3" t="n">
         <v>5</v>
       </c>
@@ -1121,18 +1673,38 @@
           <t>加熱碳化後殘留黑色物質是？</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>氫</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>無機</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
         <is>
           <t>碳</t>
         </is>
       </c>
-      <c r="D7" s="4" t="inlineStr">
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>鍵結</t>
+        </is>
+      </c>
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
         <is>
           <t>殘留</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="34" customHeight="1">
+    <row r="8" ht="40" customHeight="1">
       <c r="A8" s="6" t="n">
         <v>6</v>
       </c>
@@ -1141,18 +1713,38 @@
           <t>有機物普遍可燃的原因？</t>
         </is>
       </c>
-      <c r="C8" s="8" t="inlineStr">
+      <c r="C8" s="7" t="inlineStr">
+        <is>
+          <t>傳統分類將其歸無機</t>
+        </is>
+      </c>
+      <c r="D8" s="7" t="inlineStr">
+        <is>
+          <t>前者含碳有機物,後者無機</t>
+        </is>
+      </c>
+      <c r="E8" s="7" t="inlineStr">
+        <is>
+          <t>有機(聚合物)</t>
+        </is>
+      </c>
+      <c r="F8" s="7" t="inlineStr">
         <is>
           <t>含碳氫可與氧反應放能</t>
         </is>
       </c>
-      <c r="D8" s="7" t="inlineStr">
+      <c r="G8" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H8" s="7" t="inlineStr">
         <is>
           <t>可燃</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="34" customHeight="1">
+    <row r="9" ht="40" customHeight="1">
       <c r="A9" s="3" t="n">
         <v>7</v>
       </c>
@@ -1161,18 +1753,38 @@
           <t>如何驗證加熱產生的氣體含碳？</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>有機(聚合物)</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
         <is>
           <t>通石灰水看是否變混濁</t>
         </is>
       </c>
-      <c r="D9" s="4" t="inlineStr">
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>前者含碳有機物,後者無機</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>碳鍵結能力強可組多樣結構</t>
+        </is>
+      </c>
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
         <is>
           <t>驗證</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="34" customHeight="1">
+    <row r="10" ht="40" customHeight="1">
       <c r="A10" s="6" t="n">
         <v>8</v>
       </c>
@@ -1181,18 +1793,38 @@
           <t>有機化合物與無機的界線？</t>
         </is>
       </c>
-      <c r="C10" s="8" t="inlineStr">
+      <c r="C10" s="7" t="inlineStr">
+        <is>
+          <t>前者含碳有機物,後者無機</t>
+        </is>
+      </c>
+      <c r="D10" s="7" t="inlineStr">
         <is>
           <t>非絕對,以含碳主體概略區分</t>
         </is>
       </c>
-      <c r="D10" s="7" t="inlineStr">
+      <c r="E10" s="7" t="inlineStr">
+        <is>
+          <t>有機(聚合物)</t>
+        </is>
+      </c>
+      <c r="F10" s="7" t="inlineStr">
+        <is>
+          <t>含碳有機物加熱會碳化</t>
+        </is>
+      </c>
+      <c r="G10" s="8" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H10" s="7" t="inlineStr">
         <is>
           <t>界線</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="34" customHeight="1">
+    <row r="11" ht="40" customHeight="1">
       <c r="A11" s="3" t="n">
         <v>9</v>
       </c>
@@ -1201,18 +1833,38 @@
           <t>用蒸發皿加熱如何分辨有機與無機物？</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>有機(聚合物)</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>蒸發皿加熱看是否碳化</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
         <is>
           <t>含碳有機物加熱會碳化</t>
         </is>
       </c>
-      <c r="D11" s="4" t="inlineStr">
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>含碳氫可與氧反應放能</t>
+        </is>
+      </c>
+      <c r="G11" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
         <is>
           <t>實驗</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="34" customHeight="1">
+    <row r="12" ht="40" customHeight="1">
       <c r="A12" s="6" t="n">
         <v>10</v>
       </c>
@@ -1221,12 +1873,32 @@
           <t>為何有機化合物種類特別多？</t>
         </is>
       </c>
-      <c r="C12" s="8" t="inlineStr">
+      <c r="C12" s="7" t="inlineStr">
+        <is>
+          <t>含碳有機物加熱會碳化</t>
+        </is>
+      </c>
+      <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>前者含碳有機物,後者無機</t>
+        </is>
+      </c>
+      <c r="E12" s="7" t="inlineStr">
+        <is>
+          <t>含碳氫可與氧反應放能</t>
+        </is>
+      </c>
+      <c r="F12" s="7" t="inlineStr">
         <is>
           <t>碳鍵結能力強可組多樣結構</t>
         </is>
       </c>
-      <c r="D12" s="7" t="inlineStr">
+      <c r="G12" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H12" s="7" t="inlineStr">
         <is>
           <t>碳鍵</t>
         </is>
@@ -1234,7 +1906,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A1:H1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/02_加值成品/八下/八下5-1_三種難度測驗卷.xlsx
+++ b/02_加值成品/八下/八下5-1_三種難度測驗卷.xlsx
@@ -588,7 +588,7 @@
       </c>
       <c r="H3" s="4" t="inlineStr">
         <is>
-          <t>含碳</t>
+          <t>含碳：有機化合物這個大家族，最主要就是以碳原子為骨架組成的</t>
         </is>
       </c>
     </row>
@@ -628,7 +628,7 @@
       </c>
       <c r="H4" s="7" t="inlineStr">
         <is>
-          <t>碳氫</t>
+          <t>碳氫：大部分有機化合物除了碳，還會搭配氫原子一起組成分子</t>
         </is>
       </c>
     </row>
@@ -668,7 +668,7 @@
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>有機</t>
+          <t>有機：麵粉屬於有機物，用力加熱後裡面的碳會留下來變成焦黑的顏色</t>
         </is>
       </c>
     </row>
@@ -708,7 +708,7 @@
       </c>
       <c r="H6" s="7" t="inlineStr">
         <is>
-          <t>無機</t>
+          <t>無機：食鹽不含碳，屬於無機物，就算加熱也不會出現變黑碳化的現象</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>成鏈</t>
+          <t>成鏈：碳原子有個特別的本領，能一個接一個互相連接，組成長長的鏈狀結構</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="H8" s="7" t="inlineStr">
         <is>
-          <t>有機物</t>
+          <t>有機物：物質加熱後表面變黑，通常代表裡面含有碳，是有機物的一個特徵</t>
         </is>
       </c>
     </row>
@@ -828,7 +828,7 @@
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>有機</t>
+          <t>有機：糖屬於有機物，加熱過程中糖分子分解，碳留下來讓顏色變成焦褐色</t>
         </is>
       </c>
     </row>
@@ -868,7 +868,7 @@
       </c>
       <c r="H10" s="7" t="inlineStr">
         <is>
-          <t>可燃</t>
+          <t>可燃：因為有機物大多含有碳和氫，這些元素能和氧氣反應燃燒，放出熱和光</t>
         </is>
       </c>
     </row>
@@ -908,7 +908,7 @@
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>含碳</t>
+          <t>含碳：有機化合物是指主要由碳元素組成骨架的化合物，這是有機物最基本的判別特徵</t>
         </is>
       </c>
     </row>
@@ -948,7 +948,7 @@
       </c>
       <c r="H12" s="7" t="inlineStr">
         <is>
-          <t>有機</t>
+          <t>有機：麵粉屬於有機物，加熱過度時內部的碳骨架會分解，留下黑色的碳，這個現象稱為碳化</t>
         </is>
       </c>
     </row>
@@ -1064,7 +1064,7 @@
       </c>
       <c r="H3" s="4" t="inlineStr">
         <is>
-          <t>含碳</t>
+          <t>含碳：糖粉裡含有碳，持續加熱後水分和其他成分逐漸分解，留下焦黑的碳</t>
         </is>
       </c>
     </row>
@@ -1104,7 +1104,7 @@
       </c>
       <c r="H4" s="7" t="inlineStr">
         <is>
-          <t>無機</t>
+          <t>無機：食鹽本身不含碳原子，屬於無機物，加熱頂多熔化，不會出現碳化變黑的現象</t>
         </is>
       </c>
     </row>
@@ -1144,7 +1144,7 @@
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>種類多</t>
+          <t>種類多：碳原子能組成長鏈也能組成環狀結構，變化非常多，所以有機物種類特別龐大</t>
         </is>
       </c>
     </row>
@@ -1184,7 +1184,7 @@
       </c>
       <c r="H6" s="7" t="inlineStr">
         <is>
-          <t>歸類</t>
+          <t>歸類：雖然二氧化碳含有碳原子，但依照化學上的傳統分類方式，它被歸類為無機物</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>組成</t>
+          <t>組成：大多數有機化合物是由碳、氫這兩種元素為主，再搭配一些氧和氮組成的</t>
         </is>
       </c>
     </row>
@@ -1264,7 +1264,7 @@
       </c>
       <c r="H8" s="7" t="inlineStr">
         <is>
-          <t>含碳</t>
+          <t>含碳：酒精的分子結構裡含有碳原子，符合有機化合物以碳為主體的定義，所以是有機物</t>
         </is>
       </c>
     </row>
@@ -1304,7 +1304,7 @@
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>含碳</t>
+          <t>含碳：塑膠是由許多含碳的小分子重複連接而成的巨大分子，屬於有機聚合物</t>
         </is>
       </c>
     </row>
@@ -1344,7 +1344,7 @@
       </c>
       <c r="H10" s="7" t="inlineStr">
         <is>
-          <t>特徵</t>
+          <t>特徵：因為含碳，加熱後容易分解留下黑色的碳，這是有機物很常見的一種判別特徵</t>
         </is>
       </c>
     </row>
@@ -1384,7 +1384,7 @@
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>無機</t>
+          <t>無機：食鹽(氯化鈉)不含碳骨架，屬於無機物，加熱時不會發生像有機物那樣的碳化現象</t>
         </is>
       </c>
     </row>
@@ -1424,7 +1424,7 @@
       </c>
       <c r="H12" s="7" t="inlineStr">
         <is>
-          <t>鍵結</t>
+          <t>鍵結：碳原子有很強的自我鍵結能力，能一個接一個連接形成長鏈狀或環狀的骨架結構，這是有機化合物種類繁多的重要原因</t>
         </is>
       </c>
     </row>
@@ -1540,7 +1540,7 @@
       </c>
       <c r="H3" s="4" t="inlineStr">
         <is>
-          <t>實驗</t>
+          <t>實驗：把三種粉末分別放進蒸發皿加熱，觀察哪些出現焦黑碳化，藉此判斷是不是含碳的有機物</t>
         </is>
       </c>
     </row>
@@ -1580,7 +1580,7 @@
       </c>
       <c r="H4" s="7" t="inlineStr">
         <is>
-          <t>組成</t>
+          <t>組成：麵粉和糖的分子結構裡含有碳原子屬於有機物，加熱時碳會留下變黑；食鹽不含碳所以不會碳化</t>
         </is>
       </c>
     </row>
@@ -1620,7 +1620,7 @@
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>鍵結</t>
+          <t>鍵結：碳原子可以和好幾個原子（包括自己）同時牢固地連接，組合方式非常多樣，造就有機物種類眾多</t>
         </is>
       </c>
     </row>
@@ -1660,7 +1660,7 @@
       </c>
       <c r="H6" s="7" t="inlineStr">
         <is>
-          <t>慣例</t>
+          <t>慣例：雖然二氧化碳含有碳原子，但因為結構簡單且性質接近無機物，化學界慣例上把它歸類為無機物</t>
         </is>
       </c>
     </row>
@@ -1700,7 +1700,7 @@
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>殘留</t>
+          <t>殘留：有機物加熱分解後，其他成分揮發或反應掉，最後留下來的黑色固體就是碳</t>
         </is>
       </c>
     </row>
@@ -1740,7 +1740,7 @@
       </c>
       <c r="H8" s="7" t="inlineStr">
         <is>
-          <t>可燃</t>
+          <t>可燃：有機物裡的碳和氫原子能和空氣中的氧氣進行反應，過程中釋放出能量，所以容易燃燒</t>
         </is>
       </c>
     </row>
@@ -1780,7 +1780,7 @@
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>驗證</t>
+          <t>驗證：把加熱時產生的氣體導入澄清石灰水，如果石灰水變得混濁，就能證實氣體裡含有碳（二氧化碳）</t>
         </is>
       </c>
     </row>
@@ -1820,7 +1820,7 @@
       </c>
       <c r="H10" s="7" t="inlineStr">
         <is>
-          <t>界線</t>
+          <t>界線：有機和無機的分類其實不是絕對的，大致上是以含碳為主體、又有一定的性質特徵來區分的</t>
         </is>
       </c>
     </row>
@@ -1860,7 +1860,7 @@
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>實驗</t>
+          <t>實驗：把樣品放在蒸發皿上加熱，如果是含碳的有機物，加熱到一定溫度會逐漸變黑碳化；無機物則通常不會出現這種碳化現象，可以用這個方法初步分辨</t>
         </is>
       </c>
     </row>
@@ -1900,7 +1900,7 @@
       </c>
       <c r="H12" s="7" t="inlineStr">
         <is>
-          <t>碳鍵</t>
+          <t>碳鍵：碳原子可以和其他碳原子或多種元素形成穩定的鍵結，組合出鏈狀、環狀等各式各樣複雜的結構，因此有機化合物的種類非常龐大多樣</t>
         </is>
       </c>
     </row>

--- a/02_加值成品/八下/八下5-1_三種難度測驗卷.xlsx
+++ b/02_加值成品/八下/八下5-1_三種難度測驗卷.xlsx
@@ -563,7 +563,7 @@
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>物質多樣性</t>
+          <t>無機物</t>
         </is>
       </c>
       <c r="D3" s="4" t="inlineStr">
@@ -578,7 +578,7 @@
       </c>
       <c r="F3" s="4" t="inlineStr">
         <is>
-          <t>碳化</t>
+          <t>燃燒</t>
         </is>
       </c>
       <c r="G3" s="5" t="inlineStr">
@@ -603,12 +603,12 @@
       </c>
       <c r="C4" s="7" t="inlineStr">
         <is>
-          <t>碳(碳化)</t>
+          <t>碳化</t>
         </is>
       </c>
       <c r="D4" s="7" t="inlineStr">
         <is>
-          <t>焦黑碳化</t>
+          <t>不會</t>
         </is>
       </c>
       <c r="E4" s="7" t="inlineStr">
@@ -618,7 +618,7 @@
       </c>
       <c r="F4" s="7" t="inlineStr">
         <is>
-          <t>無機</t>
+          <t>碳</t>
         </is>
       </c>
       <c r="G4" s="8" t="inlineStr">
@@ -643,17 +643,17 @@
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>物質多樣性</t>
+          <t>碳氫氧氮</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>鍵結</t>
+          <t>碳(碳化)</t>
         </is>
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>碳化</t>
+          <t>氫</t>
         </is>
       </c>
       <c r="F5" s="4" t="inlineStr">
@@ -768,17 +768,17 @@
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
-          <t>焦黑(碳化)</t>
+          <t>無機物</t>
         </is>
       </c>
       <c r="E8" s="7" t="inlineStr">
         <is>
-          <t>不會</t>
+          <t>氫</t>
         </is>
       </c>
       <c r="F8" s="7" t="inlineStr">
         <is>
-          <t>焦黑碳化</t>
+          <t>長鏈或環</t>
         </is>
       </c>
       <c r="G8" s="8" t="inlineStr">
@@ -808,17 +808,17 @@
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>碳氫氧氮</t>
+          <t>有機物</t>
         </is>
       </c>
       <c r="E9" s="4" t="inlineStr">
         <is>
-          <t>不會</t>
+          <t>燃燒</t>
         </is>
       </c>
       <c r="F9" s="4" t="inlineStr">
         <is>
-          <t>燃燒</t>
+          <t>無機</t>
         </is>
       </c>
       <c r="G9" s="5" t="inlineStr">
@@ -888,17 +888,17 @@
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>無機</t>
+          <t>鍵結</t>
         </is>
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
-          <t>焦黑(碳化)</t>
+          <t>長鏈或環</t>
         </is>
       </c>
       <c r="F11" s="4" t="inlineStr">
         <is>
-          <t>焦黑碳化</t>
+          <t>物質多樣性</t>
         </is>
       </c>
       <c r="G11" s="5" t="inlineStr">
@@ -928,17 +928,17 @@
       </c>
       <c r="D12" s="7" t="inlineStr">
         <is>
-          <t>無機物</t>
+          <t>鍵結</t>
         </is>
       </c>
       <c r="E12" s="7" t="inlineStr">
         <is>
-          <t>無機</t>
+          <t>氫</t>
         </is>
       </c>
       <c r="F12" s="7" t="inlineStr">
         <is>
-          <t>不會</t>
+          <t>焦黑碳化</t>
         </is>
       </c>
       <c r="G12" s="8" t="inlineStr">
@@ -1039,17 +1039,17 @@
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>碳氫氧氮</t>
+          <t>氫</t>
         </is>
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
+          <t>焦黑碳化</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
           <t>燃燒</t>
-        </is>
-      </c>
-      <c r="E3" s="4" t="inlineStr">
-        <is>
-          <t>物質多樣性</t>
         </is>
       </c>
       <c r="F3" s="4" t="inlineStr">
@@ -1159,7 +1159,7 @@
       </c>
       <c r="C6" s="7" t="inlineStr">
         <is>
-          <t>焦黑(碳化)</t>
+          <t>碳化</t>
         </is>
       </c>
       <c r="D6" s="7" t="inlineStr">
@@ -1169,12 +1169,12 @@
       </c>
       <c r="E6" s="7" t="inlineStr">
         <is>
-          <t>碳</t>
+          <t>氫</t>
         </is>
       </c>
       <c r="F6" s="7" t="inlineStr">
         <is>
-          <t>長鏈或環</t>
+          <t>不會</t>
         </is>
       </c>
       <c r="G6" s="8" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>不會</t>
+          <t>燃燒</t>
         </is>
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t>長鏈或環</t>
+          <t>焦黑碳化</t>
         </is>
       </c>
       <c r="F7" s="4" t="inlineStr">
@@ -1364,17 +1364,17 @@
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>有機物</t>
         </is>
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
-          <t>有機物</t>
+          <t>不會</t>
         </is>
       </c>
       <c r="F11" s="4" t="inlineStr">
         <is>
-          <t>氫</t>
+          <t>燃燒</t>
         </is>
       </c>
       <c r="G11" s="5" t="inlineStr">
@@ -1675,22 +1675,22 @@
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
+          <t>燃燒</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>無機物</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>碳</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
           <t>氫</t>
-        </is>
-      </c>
-      <c r="D7" s="4" t="inlineStr">
-        <is>
-          <t>無機</t>
-        </is>
-      </c>
-      <c r="E7" s="4" t="inlineStr">
-        <is>
-          <t>碳</t>
-        </is>
-      </c>
-      <c r="F7" s="4" t="inlineStr">
-        <is>
-          <t>鍵結</t>
         </is>
       </c>
       <c r="G7" s="5" t="inlineStr">
